--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_178_R18.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_178_R18.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.623</v>
+        <v>4.7003</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9329</v>
+        <v>4.6406</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3099</v>
+        <v>0.0598</v>
       </c>
       <c r="G2" t="n">
         <v>2.603</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.444</v>
+        <v>-0.3666</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3497</v>
+        <v>0.358</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0943</v>
+        <v>-0.7246</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7936</v>
+        <v>3.0877</v>
       </c>
       <c r="E3" t="n">
-        <v>1.757</v>
+        <v>2.1855</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0366</v>
+        <v>0.9022</v>
       </c>
       <c r="G3" t="n">
         <v>4.8993</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.268</v>
+        <v>0.5621</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.051</v>
+        <v>0.3776</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3189</v>
+        <v>0.1845</v>
       </c>
       <c r="V3" t="n">
         <v>-1.214</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2973</v>
+        <v>1.2035</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3636</v>
+        <v>1.7738</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.5703</v>
       </c>
       <c r="G4" t="n">
         <v>0.9308</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7945</v>
+        <v>0.7007</v>
       </c>
       <c r="T4" t="n">
-        <v>1.447</v>
+        <v>0.8573</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3475</v>
+        <v>-0.1566</v>
       </c>
       <c r="V4" t="n">
         <v>-1.3558</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5716</v>
+        <v>1.167</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0844</v>
+        <v>0.6126</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4871</v>
+        <v>0.5544</v>
       </c>
       <c r="G5" t="n">
         <v>0.5911</v>
@@ -844,13 +844,13 @@
         <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7486</v>
+        <v>0.344</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9436</v>
+        <v>0.4718</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.195</v>
+        <v>-0.1278</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2254</v>
+        <v>0.822</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4825</v>
+        <v>-0.054</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7079</v>
+        <v>0.8759</v>
       </c>
       <c r="G6" t="n">
         <v>0.513</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0556</v>
+        <v>-0.4591</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3576</v>
+        <v>0.0709</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.698</v>
+        <v>-0.53</v>
       </c>
       <c r="V6" t="n">
         <v>0.5361</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3889</v>
+        <v>0.7728</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5101</v>
+        <v>2.3357</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.899</v>
+        <v>-1.5629</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4667</v>
@@ -1000,13 +1000,13 @@
         <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8373</v>
+        <v>0.3244</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1766</v>
+        <v>0.6491</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6607</v>
+        <v>-0.3246</v>
       </c>
       <c r="V7" t="n">
         <v>2.5387</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1344</v>
+        <v>-1.1929</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8895</v>
+        <v>-1.3431</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7551</v>
+        <v>0.1502</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6887</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0903</v>
+        <v>1.0319</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0395</v>
+        <v>0.586</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0508</v>
+        <v>0.4459</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2775</v>
+        <v>-2.7197</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6275</v>
+        <v>0.0508</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.905</v>
+        <v>-2.7705</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6388</v>
@@ -1156,13 +1156,13 @@
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6138</v>
+        <v>1.1716</v>
       </c>
       <c r="T9" t="n">
-        <v>3.0355</v>
+        <v>1.4589</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4217</v>
+        <v>-0.2873</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7886</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2975</v>
+        <v>-2.8525</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2776</v>
+        <v>0.0329</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0199</v>
+        <v>-2.8855</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2435</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.036</v>
+        <v>0.409</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3857</v>
+        <v>0.6963</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4217</v>
+        <v>-0.2873</v>
       </c>
       <c r="V10" t="n">
         <v>0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.356</v>
+        <v>-3.5583</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1224</v>
+        <v>-0.1135</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4784</v>
+        <v>-3.4448</v>
       </c>
       <c r="G11" t="n">
         <v>-2.871</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1233</v>
+        <v>0.921</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9831</v>
+        <v>0.7472</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1401</v>
+        <v>0.1737</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.056600000000001</v>
+        <v>1.4299</v>
       </c>
       <c r="E12" t="n">
-        <v>9.748300000000002</v>
+        <v>10.1213</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.691699999999999</v>
+        <v>-8.691500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3715</v>
@@ -1390,10 +1390,10 @@
         <v>13.9172</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2656</v>
+        <v>4.639</v>
       </c>
       <c r="T12" t="n">
-        <v>5.8995</v>
+        <v>6.2731</v>
       </c>
       <c r="U12" t="n">
         <v>-1.6341</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.5154</v>
+        <v>9.145099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>8.6938</v>
+        <v>9.4015</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1785</v>
+        <v>-0.2564</v>
       </c>
       <c r="G13" t="n">
         <v>12.0599</v>
@@ -1468,13 +1468,13 @@
         <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5292</v>
+        <v>-0.8995</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2696</v>
+        <v>-0.5619</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2596</v>
+        <v>-0.3376</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0085</v>
+        <v>4.6813</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0363</v>
+        <v>4.7935</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0277</v>
+        <v>-0.1122</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6774</v>
+        <v>1.9049</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1123</v>
+        <v>1.664</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4349</v>
+        <v>0.2409</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7142</v>
+        <v>3.3633</v>
       </c>
       <c r="K14" t="n">
-        <v>1.567</v>
+        <v>1.6469</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1472</v>
+        <v>1.7164</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0368</v>
+        <v>-1.4583</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4547</v>
+        <v>0.0171</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5821</v>
+        <v>-1.4755</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1171</v>
+        <v>-0.172</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8219</v>
+        <v>0.358</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2952</v>
+        <v>-0.53</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1418</v>
+        <v>1.3247</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8197</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9629</v>
+        <v>2.1412</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5576</v>
+        <v>2.437</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5947</v>
+        <v>-0.2958</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9049</v>
+        <v>-0.9538</v>
       </c>
       <c r="H15" t="n">
-        <v>1.664</v>
+        <v>-1.8606</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2409</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3633</v>
+        <v>0.873</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6469</v>
+        <v>-0.8802</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7164</v>
+        <v>1.7532</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4583</v>
+        <v>-1.8268</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0171</v>
+        <v>-0.9804</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4755</v>
+        <v>-0.8464</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8905</v>
+        <v>0.1672</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1221</v>
+        <v>0.4918</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0126</v>
+        <v>-0.3246</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3247</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
         <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7201</v>
+        <v>1.2183</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5549</v>
+        <v>1.5593</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8348</v>
+        <v>-0.341</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9538</v>
+        <v>0.6774</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8606</v>
+        <v>1.1123</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9068000000000001</v>
+        <v>-0.4349</v>
       </c>
       <c r="J16" t="n">
-        <v>0.873</v>
+        <v>1.7142</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8802</v>
+        <v>1.567</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7532</v>
+        <v>0.1472</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8268</v>
+        <v>-1.0368</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9804</v>
+        <v>-0.4547</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8464</v>
+        <v>-0.5821</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2539</v>
+        <v>1.3269</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6097</v>
+        <v>1.3449</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8637</v>
+        <v>-0.018</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.8197</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.3144</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9496</v>
+        <v>-0.0066</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8593</v>
+        <v>-0.3079</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8612</v>
+        <v>0.4762</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4598</v>
+        <v>0.155</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4015</v>
+        <v>0.3212</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.175</v>
+        <v>0.5122</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2486</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0736</v>
+        <v>0.4282</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6862</v>
+        <v>-0.036</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2112</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4751</v>
+        <v>-0.107</v>
       </c>
       <c r="P17" t="n">
         <v>0.6959</v>
@@ -1780,28 +1780,28 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2557</v>
+        <v>-0.9504</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3566</v>
+        <v>-0.2869</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1009</v>
+        <v>-0.6636</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8756</v>
+        <v>-0.3649</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2425</v>
+        <v>0.277</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6332</v>
+        <v>-0.6419</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4762</v>
+        <v>-2.507</v>
       </c>
       <c r="H18" t="n">
-        <v>0.155</v>
+        <v>-2.1691</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3212</v>
+        <v>-0.3379</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5122</v>
+        <v>-0.8092</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08400000000000001</v>
+        <v>-1.4214</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4282</v>
+        <v>0.6122</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.036</v>
+        <v>-1.6978</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.7477</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.107</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5116</v>
+        <v>0.5544</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5228</v>
+        <v>0.3541</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9889</v>
+        <v>0.2003</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>1.3558</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8919</v>
       </c>
       <c r="X18" t="n">
         <v>-0.5361</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7575</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6666</v>
+        <v>0.006</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0908</v>
+        <v>-0.5448</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.507</v>
+        <v>-0.8612</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1691</v>
+        <v>-0.4598</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3379</v>
+        <v>-0.4015</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8092</v>
+        <v>-0.175</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4214</v>
+        <v>-0.2486</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6122</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6978</v>
+        <v>-0.6862</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7477</v>
+        <v>-0.2112</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.4751</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.3734</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5895</v>
+        <v>0.4129</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2486</v>
+        <v>-0.7863</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8919</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.091</v>
+        <v>-1.8722</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3815</v>
+        <v>-2.2635</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2905</v>
+        <v>0.3913</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4965</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4055</v>
+        <v>0.6242</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4955</v>
+        <v>0.6135</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4702</v>
+        <v>-2.1842</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9947</v>
+        <v>-0.8767</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4755</v>
+        <v>-1.3075</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1287</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5012</v>
+        <v>-0.2153</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2057</v>
+        <v>-3.1169</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0698</v>
+        <v>0.5416</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.2755</v>
+        <v>-3.6585</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7916</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.11</v>
+        <v>-1.0212</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8962</v>
+        <v>-0.4244</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2138</v>
+        <v>-0.5968</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9537</v>
+        <v>-7.492</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.4213</v>
+        <v>-7.7135</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4676</v>
+        <v>0.2216</v>
       </c>
       <c r="G23" t="n">
         <v>-5.0083</v>
@@ -2248,13 +2248,13 @@
         <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4093</v>
+        <v>-0.9476</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1949</v>
+        <v>-0.4872</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2144</v>
+        <v>-0.4604</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.056500000000004</v>
+        <v>1.302500000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>8.155399999999998</v>
+        <v>8.155599999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.2119</v>
+        <v>-6.8531</v>
       </c>
       <c r="G24" t="n">
-        <v>1.371300000000001</v>
+        <v>1.371299999999999</v>
       </c>
       <c r="H24" t="n">
         <v>-7.5623</v>
@@ -2314,7 +2314,7 @@
         <v>-6.2275</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.767100000000001</v>
+        <v>-4.7671</v>
       </c>
       <c r="P24" t="n">
         <v>1.1599</v>
@@ -2326,13 +2326,13 @@
         <v>15.077</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.2656</v>
+        <v>-1.9067</v>
       </c>
       <c r="T24" t="n">
-        <v>1.634099999999999</v>
+        <v>1.634</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.8999</v>
+        <v>-3.5407</v>
       </c>
       <c r="V24" t="n">
         <v>0.6778999999999997</v>
